--- a/outputs/daily/hr_rankings_2026-08-23_remaining.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-23_remaining.xlsx
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>63.1</v>
+        <v>63.6</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>40.1</v>
       </c>
       <c r="R2" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S2" t="n">
         <v>94.90000000000001</v>
@@ -826,34 +826,30 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 3</t>
-        </is>
-      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1003,7 +999,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1068,11 +1064,11 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>59.6</v>
+        <v>60.2</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Longshot</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1092,7 +1088,7 @@
         <v>35.9</v>
       </c>
       <c r="R3" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S3" t="n">
         <v>96.59999999999999</v>
@@ -1110,34 +1106,30 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -1287,7 +1279,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1352,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>57.9</v>
+        <v>58.5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1376,7 +1368,7 @@
         <v>35.9</v>
       </c>
       <c r="R4" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -1394,34 +1386,30 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 1</t>
-        </is>
-      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -1571,7 +1559,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -1636,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>54.9</v>
+        <v>55.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1660,7 +1648,7 @@
         <v>40.1</v>
       </c>
       <c r="R5" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S5" t="n">
         <v>93.2</v>
@@ -1678,34 +1666,30 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 1 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1855,7 +1839,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -1920,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>54.5</v>
+        <v>55</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1944,7 +1928,7 @@
         <v>35.9</v>
       </c>
       <c r="R6" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S6" t="n">
         <v>86.40000000000001</v>
@@ -1962,34 +1946,30 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -2139,7 +2119,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2204,7 +2184,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>52.7</v>
+        <v>53.2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2228,7 +2208,7 @@
         <v>35.9</v>
       </c>
       <c r="R7" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S7" t="n">
         <v>93.2</v>
@@ -2246,34 +2226,30 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 1 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -2423,7 +2399,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -2488,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>52.5</v>
+        <v>53.1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2512,7 +2488,7 @@
         <v>40.1</v>
       </c>
       <c r="R8" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S8" t="n">
         <v>96.59999999999999</v>
@@ -2530,34 +2506,30 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2707,7 +2679,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -2772,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>52.3</v>
+        <v>52.9</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2796,7 +2768,7 @@
         <v>40.1</v>
       </c>
       <c r="R9" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S9" t="n">
         <v>100</v>
@@ -2814,34 +2786,30 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 1</t>
-        </is>
-      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2991,7 +2959,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -3056,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>52.2</v>
+        <v>52.8</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3080,7 +3048,7 @@
         <v>40.1</v>
       </c>
       <c r="R10" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S10" t="n">
         <v>52.4</v>
@@ -3098,34 +3066,30 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 8 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3275,7 +3239,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -3340,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>51</v>
+        <v>51.5</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3364,7 +3328,7 @@
         <v>40.1</v>
       </c>
       <c r="R11" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S11" t="n">
         <v>76.2</v>
@@ -3382,34 +3346,30 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3559,7 +3519,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -3624,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>50.4</v>
+        <v>50.9</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3648,7 +3608,7 @@
         <v>35.9</v>
       </c>
       <c r="R12" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S12" t="n">
         <v>52.4</v>
@@ -3666,34 +3626,30 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -3843,7 +3799,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -3908,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>48.6</v>
+        <v>49.2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3932,7 +3888,7 @@
         <v>40.1</v>
       </c>
       <c r="R13" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S13" t="n">
         <v>86.40000000000001</v>
@@ -3950,34 +3906,30 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4127,7 +4079,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -4192,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>45.9</v>
+        <v>46.4</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4216,7 +4168,7 @@
         <v>35.9</v>
       </c>
       <c r="R14" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S14" t="n">
         <v>76.2</v>
@@ -4234,34 +4186,30 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -4411,7 +4359,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -4476,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>44</v>
+        <v>44.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4500,7 +4448,7 @@
         <v>35</v>
       </c>
       <c r="R15" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S15" t="n">
         <v>94.90000000000001</v>
@@ -4518,34 +4466,30 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -4695,7 +4639,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -4760,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>40.5</v>
+        <v>41.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4784,7 +4728,7 @@
         <v>40.1</v>
       </c>
       <c r="R16" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S16" t="n">
         <v>64.3</v>
@@ -4800,28 +4744,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="Y16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4971,7 +4919,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -5036,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>39.1</v>
+        <v>39.6</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5060,7 +5008,7 @@
         <v>35.9</v>
       </c>
       <c r="R17" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S17" t="n">
         <v>64.3</v>
@@ -5078,34 +5026,30 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -5255,7 +5199,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -5320,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>38.4</v>
+        <v>39</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5344,7 +5288,7 @@
         <v>40.1</v>
       </c>
       <c r="R18" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S18" t="n">
         <v>44.8</v>
@@ -5362,34 +5306,30 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 9 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5539,7 +5479,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -5604,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>35.2</v>
+        <v>35.7</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5628,7 +5568,7 @@
         <v>35.9</v>
       </c>
       <c r="R19" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -5646,34 +5586,30 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -5823,7 +5759,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -6214,7 +6150,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>63.1</v>
+        <v>63.6</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6238,7 +6174,7 @@
         <v>40.1</v>
       </c>
       <c r="R2" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S2" t="n">
         <v>94.90000000000001</v>
@@ -6256,34 +6192,30 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 3</t>
-        </is>
-      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6433,7 +6365,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -6498,11 +6430,11 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>59.6</v>
+        <v>60.2</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Longshot</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -6522,7 +6454,7 @@
         <v>35.9</v>
       </c>
       <c r="R3" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S3" t="n">
         <v>96.59999999999999</v>
@@ -6540,34 +6472,30 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -6717,7 +6645,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -6782,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>57.9</v>
+        <v>58.5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6806,7 +6734,7 @@
         <v>35.9</v>
       </c>
       <c r="R4" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -6824,34 +6752,30 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 1</t>
-        </is>
-      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -7001,7 +6925,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -7066,7 +6990,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>54.9</v>
+        <v>55.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7090,7 +7014,7 @@
         <v>40.1</v>
       </c>
       <c r="R5" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S5" t="n">
         <v>93.2</v>
@@ -7108,34 +7032,30 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 1 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7285,7 +7205,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -7350,7 +7270,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>54.5</v>
+        <v>55</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7374,7 +7294,7 @@
         <v>35.9</v>
       </c>
       <c r="R6" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S6" t="n">
         <v>86.40000000000001</v>
@@ -7392,34 +7312,30 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -7569,7 +7485,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -7634,7 +7550,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>52.7</v>
+        <v>53.2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7658,7 +7574,7 @@
         <v>35.9</v>
       </c>
       <c r="R7" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S7" t="n">
         <v>93.2</v>
@@ -7676,34 +7592,30 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 1 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -7853,7 +7765,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -7918,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>52.5</v>
+        <v>53.1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7942,7 +7854,7 @@
         <v>40.1</v>
       </c>
       <c r="R8" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S8" t="n">
         <v>96.59999999999999</v>
@@ -7960,34 +7872,30 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8137,7 +8045,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -8202,7 +8110,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>52.3</v>
+        <v>52.9</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8226,7 +8134,7 @@
         <v>40.1</v>
       </c>
       <c r="R9" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S9" t="n">
         <v>100</v>
@@ -8244,34 +8152,30 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 1</t>
-        </is>
-      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8421,7 +8325,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -8486,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>52.2</v>
+        <v>52.8</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8510,7 +8414,7 @@
         <v>40.1</v>
       </c>
       <c r="R10" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S10" t="n">
         <v>52.4</v>
@@ -8528,34 +8432,30 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 8 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8705,7 +8605,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -8770,7 +8670,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>51</v>
+        <v>51.5</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8794,7 +8694,7 @@
         <v>40.1</v>
       </c>
       <c r="R11" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S11" t="n">
         <v>76.2</v>
@@ -8812,34 +8712,30 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8989,7 +8885,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -9054,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>50.4</v>
+        <v>50.9</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -9078,7 +8974,7 @@
         <v>35.9</v>
       </c>
       <c r="R12" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S12" t="n">
         <v>52.4</v>
@@ -9096,34 +8992,30 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -9273,7 +9165,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -9338,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>48.6</v>
+        <v>49.2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9362,7 +9254,7 @@
         <v>40.1</v>
       </c>
       <c r="R13" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S13" t="n">
         <v>86.40000000000001</v>
@@ -9380,34 +9272,30 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9557,7 +9445,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -9622,7 +9510,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>45.9</v>
+        <v>46.4</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9646,7 +9534,7 @@
         <v>35.9</v>
       </c>
       <c r="R14" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S14" t="n">
         <v>76.2</v>
@@ -9664,34 +9552,30 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -9841,7 +9725,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -9906,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>44</v>
+        <v>44.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9930,7 +9814,7 @@
         <v>35</v>
       </c>
       <c r="R15" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S15" t="n">
         <v>94.90000000000001</v>
@@ -9948,34 +9832,30 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -10125,7 +10005,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -10190,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>40.5</v>
+        <v>41.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10214,7 +10094,7 @@
         <v>40.1</v>
       </c>
       <c r="R16" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S16" t="n">
         <v>64.3</v>
@@ -10230,28 +10110,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="Y16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10401,7 +10285,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -10466,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>39.1</v>
+        <v>39.6</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10490,7 +10374,7 @@
         <v>35.9</v>
       </c>
       <c r="R17" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S17" t="n">
         <v>64.3</v>
@@ -10508,34 +10392,30 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -10685,7 +10565,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -10750,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>38.4</v>
+        <v>39</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10774,7 +10654,7 @@
         <v>40.1</v>
       </c>
       <c r="R18" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S18" t="n">
         <v>44.8</v>
@@ -10792,34 +10672,30 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 9 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10969,7 +10845,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -11034,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>35.2</v>
+        <v>35.7</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -11058,7 +10934,7 @@
         <v>35.9</v>
       </c>
       <c r="R19" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -11076,34 +10952,30 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -11253,7 +11125,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-08-23_remaining.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-23_remaining.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -9766,7 +9766,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -10046,7 +10046,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -10606,7 +10606,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -10886,7 +10886,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
